--- a/out/08_ISMS/SNX-ISMS-FRM-02 Security Incident Investigation Records (Rev00 DRAFT).xlsx
+++ b/out/08_ISMS/SNX-ISMS-FRM-02 Security Incident Investigation Records (Rev00 DRAFT).xlsx
@@ -15,8 +15,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chain of Custody" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Daftar'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Register'!$A$4:$V$155</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Register'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Chain of Custody'!$A$4:$K$154</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Chain of Custody'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -171,7 +174,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -316,6 +319,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -710,8 +734,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="27">
-      <c r="A4" s="30" t="inlineStr">
+    <row r="3" s="27">
+      <c r="A3" s="49" t="n"/>
+      <c r="B3" s="49" t="n"/>
+      <c r="C3" s="49" t="n"/>
+      <c r="D3" s="49" t="n"/>
+      <c r="E3" s="49" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="27">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>Nomor dokumen</t>
         </is>
@@ -721,9 +752,12 @@
           <t>SNX-ISMS-FRM-02</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="27">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="C4" s="49" t="n"/>
+      <c r="D4" s="49" t="n"/>
+      <c r="E4" s="49" t="n"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="27">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>Judul</t>
         </is>
@@ -733,9 +767,12 @@
           <t>Security Incident &amp; Investigation Records</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="27">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="C5" s="49" t="n"/>
+      <c r="D5" s="49" t="n"/>
+      <c r="E5" s="49" t="n"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="27">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
@@ -745,9 +782,12 @@
           <t>00 (Draft)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="27">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="C6" s="49" t="n"/>
+      <c r="D6" s="49" t="n"/>
+      <c r="E6" s="49" t="n"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="27">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>Tanggal draft</t>
         </is>
@@ -757,9 +797,12 @@
           <t>13 Oktober 2026</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="27">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="C7" s="49" t="n"/>
+      <c r="D7" s="49" t="n"/>
+      <c r="E7" s="49" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="27">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>Tanggal efektif</t>
         </is>
@@ -769,9 +812,12 @@
           <t>Ditetapkan saat pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="27">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="C8" s="49" t="n"/>
+      <c r="D8" s="49" t="n"/>
+      <c r="E8" s="49" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="27">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>Klasifikasi</t>
         </is>
@@ -781,9 +827,12 @@
           <t>RESTRICTED (Internal)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="27">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C9" s="49" t="n"/>
+      <c r="D9" s="49" t="n"/>
+      <c r="E9" s="49" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="27">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>Pemilik dokumen</t>
         </is>
@@ -793,9 +842,12 @@
           <t>Lead SOC</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="27">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="C10" s="49" t="n"/>
+      <c r="D10" s="49" t="n"/>
+      <c r="E10" s="49" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="27">
+      <c r="A11" s="47" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
@@ -805,9 +857,12 @@
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="27">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="C11" s="49" t="n"/>
+      <c r="D11" s="49" t="n"/>
+      <c r="E11" s="49" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="27">
+      <c r="A12" s="47" t="inlineStr">
         <is>
           <t>Acuan ISO 9001:2015</t>
         </is>
@@ -817,9 +872,12 @@
           <t>Klausul 10.2</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="27">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="C12" s="49" t="n"/>
+      <c r="D12" s="49" t="n"/>
+      <c r="E12" s="49" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="27">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>Acuan ISO/IEC 27001:2022</t>
         </is>
@@ -829,9 +887,12 @@
           <t>Annex A 5.25, 5.26, 5.27, 5.28</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="27">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="C13" s="49" t="n"/>
+      <c r="D13" s="49" t="n"/>
+      <c r="E13" s="49" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="27">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>Masa simpan record</t>
         </is>
@@ -841,64 +902,90 @@
           <t>5 tahun</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="23.85" customHeight="1" s="27">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="C14" s="49" t="n"/>
+      <c r="D14" s="49" t="n"/>
+      <c r="E14" s="49" t="n"/>
+    </row>
+    <row r="15" ht="43.5" customHeight="1" s="27">
+      <c r="A15" s="47" t="inlineStr">
         <is>
           <t>Tujuan</t>
         </is>
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>Register insiden keamanan informasi, catatan investigasi, dan chain of custody bukti. Prosedur dan definisi severity P1 sampai P4 ada di SNX-ISMS-SOP-01.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="27">
-      <c r="A17" s="32" t="inlineStr">
+          <t>Mencatat insiden keamanan informasi, hasil investigasi, dan chain of custody bukti. Prosedur dan definisi severity P1 sampai P4 mengikuti SNX-ISMS-SOP-01.</t>
+        </is>
+      </c>
+      <c r="C15" s="49" t="n"/>
+      <c r="D15" s="49" t="n"/>
+      <c r="E15" s="49" t="n"/>
+    </row>
+    <row r="16" s="27">
+      <c r="A16" s="49" t="n"/>
+      <c r="B16" s="49" t="n"/>
+      <c r="C16" s="49" t="n"/>
+      <c r="D16" s="49" t="n"/>
+      <c r="E16" s="49" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="27">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>Cara pakai</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="27">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="B17" s="49" t="n"/>
+      <c r="C17" s="49" t="n"/>
+      <c r="D17" s="49" t="n"/>
+      <c r="E17" s="49" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="27">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>Satu baris per insiden keamanan di sheet Register; nomor SIR-YYYY-NNN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="27">
-      <c r="A19" s="33" t="inlineStr">
+          <t>Isi satu baris untuk setiap insiden keamanan di sheet Register, dengan nomor SIR-YYYY-NNN.</t>
+        </is>
+      </c>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="27">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>Jam ke containment dan ke pulih dihitung otomatis dari waktu deteksi, 1 desimal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="23.85" customHeight="1" s="27">
-      <c r="A20" s="33" t="inlineStr">
+          <t>Kolom Jam ke containment dan Jam ke pulih terisi otomatis dari waktu deteksi, dengan 1 desimal.</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+      <c r="E19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="57" customHeight="1" s="27">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
       <c r="B20" s="34" t="inlineStr">
         <is>
-          <t>Bila data pribadi terlibat, kolom Notifikasi PDP menandai wajib dikaji dengan batas 3 x 24 jam dari waktu deteksi. Direktur (COO) dan Legal memutuskan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="23.85" customHeight="1" s="27">
-      <c r="A21" s="33" t="inlineStr">
+          <t>Jika data pribadi terlibat, kolom Notifikasi PDP menandai insiden itu wajib dikaji, dengan batas 3 x 24 jam sejak waktu deteksi. Keputusan notifikasi diambil Direktur (COO) bersama Legal.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="27">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
@@ -908,81 +995,118 @@
           <t>Untuk insiden P1 dan P2, salin sheet Investigasi per insiden dan isi Chain of Custody untuk setiap bukti.</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="27">
-      <c r="A22" s="33" t="inlineStr">
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1" s="27">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
       <c r="B22" s="34" t="inlineStr">
         <is>
-          <t>Laporan insiden ke pelanggan memakai format laporan insiden baku.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="27">
-      <c r="A24" s="32" t="inlineStr">
+          <t>Gunakan format laporan insiden baku untuk laporan insiden ke pelanggan.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
+    </row>
+    <row r="23" s="27">
+      <c r="A23" s="49" t="n"/>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="27">
+      <c r="A24" s="50" t="inlineStr">
         <is>
           <t>Legenda warna</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="27">
-      <c r="A25" s="35" t="n"/>
-      <c r="B25" s="33" t="inlineStr">
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="27">
+      <c r="A25" s="48" t="n"/>
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>Sel input: diisi pengguna</t>
         </is>
       </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+      <c r="E25" s="49" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="27">
-      <c r="A26" s="36" t="n"/>
-      <c r="B26" s="33" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="27">
-      <c r="A27" s="37" t="n"/>
-      <c r="B27" s="33" t="inlineStr">
+      <c r="A26" s="51" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+      <c r="E26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" s="27">
+      <c r="A27" s="52" t="n"/>
+      <c r="B27" s="34" t="inlineStr">
         <is>
           <t>Sel rumus: jangan diubah</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="27">
-      <c r="A29" s="32" t="inlineStr">
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+      <c r="E27" s="49" t="n"/>
+    </row>
+    <row r="28" s="27">
+      <c r="A28" s="49" t="n"/>
+      <c r="B28" s="49" t="n"/>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+      <c r="E28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="27">
+      <c r="A29" s="50" t="inlineStr">
         <is>
           <t>Riwayat revisi</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="27">
-      <c r="A30" s="38" t="inlineStr">
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+      <c r="E29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" s="27">
+      <c r="A30" s="42" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
       </c>
-      <c r="B30" s="38" t="inlineStr">
+      <c r="B30" s="42" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
-      <c r="C30" s="38" t="inlineStr">
+      <c r="C30" s="42" t="inlineStr">
         <is>
           <t>Uraian perubahan</t>
         </is>
       </c>
-      <c r="D30" s="38" t="inlineStr">
+      <c r="D30" s="42" t="inlineStr">
         <is>
           <t>Disusun</t>
         </is>
       </c>
-      <c r="E30" s="38" t="inlineStr">
+      <c r="E30" s="42" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="23.85" customHeight="1" s="27">
+    <row r="31" ht="30" customHeight="1" s="27">
       <c r="A31" s="31" t="inlineStr">
         <is>
           <t>00</t>
@@ -1016,77 +1140,91 @@
       <c r="D32" s="31" t="n"/>
       <c r="E32" s="31" t="n"/>
     </row>
-    <row r="33"/>
-    <row r="34" ht="15" customHeight="1" s="27">
-      <c r="A34" s="32" t="inlineStr">
+    <row r="33" s="27">
+      <c r="A33" s="49" t="n"/>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+      <c r="E33" s="49" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="27">
+      <c r="A34" s="50" t="inlineStr">
         <is>
           <t>Pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="27">
-      <c r="A35" s="38" t="inlineStr">
+      <c r="B34" s="49" t="n"/>
+      <c r="C34" s="49" t="n"/>
+      <c r="D34" s="49" t="n"/>
+      <c r="E34" s="49" t="n"/>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" s="27">
+      <c r="A35" s="42" t="inlineStr">
         <is>
           <t>Peran</t>
         </is>
       </c>
-      <c r="B35" s="38" t="inlineStr">
+      <c r="B35" s="42" t="inlineStr">
         <is>
           <t>Nama dan jabatan</t>
         </is>
       </c>
-      <c r="C35" s="38" t="inlineStr">
+      <c r="C35" s="42" t="inlineStr">
         <is>
           <t>Tanda tangan</t>
         </is>
       </c>
-      <c r="D35" s="38" t="inlineStr">
+      <c r="D35" s="42" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
+      <c r="E35" s="49" t="n"/>
     </row>
     <row r="36" ht="27.75" customHeight="1" s="27">
-      <c r="A36" s="39" t="inlineStr">
+      <c r="A36" s="31" t="inlineStr">
         <is>
           <t>Disusun oleh</t>
         </is>
       </c>
-      <c r="B36" s="39" t="inlineStr">
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>Erik Dwi Yanto / Technical/Operation Engineer L1</t>
         </is>
       </c>
-      <c r="C36" s="39" t="n"/>
-      <c r="D36" s="39" t="n"/>
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="31" t="n"/>
+      <c r="E36" s="49" t="n"/>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="27">
-      <c r="A37" s="39" t="inlineStr">
+      <c r="A37" s="31" t="inlineStr">
         <is>
           <t>Diperiksa oleh</t>
         </is>
       </c>
-      <c r="B37" s="39" t="inlineStr">
+      <c r="B37" s="31" t="inlineStr">
         <is>
           <t>Fani Fatullah / VP Tech Operation and Services</t>
         </is>
       </c>
-      <c r="C37" s="39" t="n"/>
-      <c r="D37" s="39" t="n"/>
+      <c r="C37" s="31" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="49" t="n"/>
     </row>
     <row r="38" ht="27.75" customHeight="1" s="27">
-      <c r="A38" s="39" t="inlineStr">
+      <c r="A38" s="31" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
       </c>
-      <c r="B38" s="39" t="inlineStr">
+      <c r="B38" s="31" t="inlineStr">
         <is>
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-      <c r="C38" s="39" t="n"/>
-      <c r="D38" s="39" t="n"/>
+      <c r="C38" s="31" t="n"/>
+      <c r="D38" s="31" t="n"/>
+      <c r="E38" s="49" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1130,207 +1268,231 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="25" customWidth="1" style="26" min="1" max="1"/>
     <col width="16" customWidth="1" style="26" min="2" max="4"/>
+    <col width="13" customWidth="1" style="27" min="3" max="3"/>
+    <col width="13" customWidth="1" style="27" min="4" max="4"/>
     <col width="20" customWidth="1" style="26" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="27">
-      <c r="A1" s="41" t="inlineStr">
+    <row r="1" ht="16.5" customHeight="1" s="27">
+      <c r="A1" s="53" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="B1" s="41" t="inlineStr">
+      <c r="B1" s="53" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="C1" s="41" t="inlineStr">
+      <c r="C1" s="53" t="inlineStr">
         <is>
           <t>YaTidak</t>
         </is>
       </c>
-      <c r="D1" s="41" t="inlineStr">
+      <c r="D1" s="53" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E1" s="41" t="inlineStr">
+      <c r="E1" s="53" t="inlineStr">
         <is>
           <t>Sumber</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="27">
-      <c r="A2" s="33" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="27">
+      <c r="A2" s="54" t="inlineStr">
         <is>
           <t>Malware atau ransomware</t>
         </is>
       </c>
-      <c r="B2" s="33" t="inlineStr">
+      <c r="B2" s="54" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C2" s="33" t="inlineStr">
+      <c r="C2" s="54" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="D2" s="33" t="inlineStr">
+      <c r="D2" s="54" t="inlineStr">
         <is>
           <t>Investigasi</t>
         </is>
       </c>
-      <c r="E2" s="33" t="inlineStr">
+      <c r="E2" s="54" t="inlineStr">
         <is>
           <t>SIEM atau Wazuh</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="27">
-      <c r="A3" s="33" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="27">
+      <c r="A3" s="54" t="inlineStr">
         <is>
           <t>Webshell atau backdoor</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="54" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C3" s="33" t="inlineStr">
+      <c r="C3" s="54" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="D3" s="33" t="inlineStr">
+      <c r="D3" s="54" t="inlineStr">
         <is>
           <t>Containment</t>
         </is>
       </c>
-      <c r="E3" s="33" t="inlineStr">
+      <c r="E3" s="54" t="inlineStr">
         <is>
           <t>WAF</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="27">
-      <c r="A4" s="33" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="27">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>Akses tidak sah</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="54" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
+      <c r="C4" s="55" t="n"/>
+      <c r="D4" s="54" t="inlineStr">
         <is>
           <t>Eradication</t>
         </is>
       </c>
-      <c r="E4" s="33" t="inlineStr">
+      <c r="E4" s="54" t="inlineStr">
         <is>
           <t>EDR atau antivirus</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="27">
-      <c r="A5" s="33" t="inlineStr">
+    <row r="5" ht="16.5" customHeight="1" s="27">
+      <c r="A5" s="54" t="inlineStr">
         <is>
           <t>Kebocoran data</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="54" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="C5" s="55" t="n"/>
+      <c r="D5" s="54" t="inlineStr">
         <is>
           <t>Pemulihan</t>
         </is>
       </c>
-      <c r="E5" s="33" t="inlineStr">
+      <c r="E5" s="54" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="27">
-      <c r="A6" s="33" t="inlineStr">
+    <row r="6" ht="16.5" customHeight="1" s="27">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>Phishing</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="B6" s="55" t="n"/>
+      <c r="C6" s="55" t="n"/>
+      <c r="D6" s="54" t="inlineStr">
         <is>
           <t>Ditutup</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="54" t="inlineStr">
         <is>
           <t>Laporan pelanggan</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="27">
-      <c r="A7" s="33" t="inlineStr">
+    <row r="7" ht="16.5" customHeight="1" s="27">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t>DDoS</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="B7" s="55" t="n"/>
+      <c r="C7" s="55" t="n"/>
+      <c r="D7" s="55" t="n"/>
+      <c r="E7" s="54" t="inlineStr">
         <is>
           <t>Laporan personel</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="27">
-      <c r="A8" s="33" t="inlineStr">
+    <row r="8" ht="16.5" customHeight="1" s="27">
+      <c r="A8" s="54" t="inlineStr">
         <is>
           <t>Kredensial terpapar</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="B8" s="55" t="n"/>
+      <c r="C8" s="55" t="n"/>
+      <c r="D8" s="55" t="n"/>
+      <c r="E8" s="54" t="inlineStr">
         <is>
           <t>Pihak ketiga</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="27">
-      <c r="A9" s="33" t="inlineStr">
+    <row r="9" ht="16.5" customHeight="1" s="27">
+      <c r="A9" s="54" t="inlineStr">
         <is>
           <t>Pelanggaran kebijakan</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="27">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="B9" s="55" t="n"/>
+      <c r="C9" s="55" t="n"/>
+      <c r="D9" s="55" t="n"/>
+      <c r="E9" s="55" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="27">
+      <c r="A10" s="54" t="inlineStr">
         <is>
           <t>Kehilangan perangkat</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="27">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="B10" s="55" t="n"/>
+      <c r="C10" s="55" t="n"/>
+      <c r="D10" s="55" t="n"/>
+      <c r="E10" s="55" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="27">
+      <c r="A11" s="54" t="inlineStr">
         <is>
           <t>Lainnya</t>
         </is>
       </c>
+      <c r="B11" s="55" t="n"/>
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="55" t="n"/>
+      <c r="E11" s="55" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1346,17 +1508,23 @@
     <col width="13" customWidth="1" style="26" min="1" max="1"/>
     <col width="15" customWidth="1" style="26" min="2" max="2"/>
     <col width="13" customWidth="1" style="26" min="3" max="4"/>
+    <col width="13" customWidth="1" style="27" min="4" max="4"/>
     <col width="26" customWidth="1" style="26" min="5" max="5"/>
-    <col width="13" customWidth="1" style="26" min="6" max="6"/>
+    <col width="14" customWidth="1" style="26" min="6" max="6"/>
     <col width="16" customWidth="1" style="26" min="7" max="7"/>
-    <col width="8" customWidth="1" style="26" min="8" max="9"/>
-    <col width="9" customWidth="1" style="26" min="10" max="10"/>
+    <col width="12" customWidth="1" style="26" min="8" max="9"/>
+    <col width="14" customWidth="1" style="27" min="9" max="9"/>
+    <col width="12" customWidth="1" style="26" min="10" max="10"/>
     <col width="32" customWidth="1" style="26" min="11" max="11"/>
-    <col width="15" customWidth="1" style="26" min="12" max="13"/>
-    <col width="8" customWidth="1" style="26" min="14" max="15"/>
-    <col width="14" customWidth="1" style="26" min="16" max="16"/>
+    <col width="17" customWidth="1" style="26" min="12" max="13"/>
+    <col width="13" customWidth="1" style="27" min="13" max="13"/>
+    <col width="17" customWidth="1" style="26" min="14" max="15"/>
+    <col width="13" customWidth="1" style="27" min="15" max="15"/>
+    <col width="15" customWidth="1" style="26" min="16" max="16"/>
     <col width="11" customWidth="1" style="26" min="17" max="19"/>
-    <col width="9" customWidth="1" style="26" min="20" max="20"/>
+    <col width="14" customWidth="1" style="27" min="18" max="18"/>
+    <col width="13" customWidth="1" style="27" min="19" max="19"/>
+    <col width="10" customWidth="1" style="26" min="20" max="20"/>
     <col width="30" customWidth="1" style="26" min="21" max="21"/>
     <col width="12" customWidth="1" style="26" min="22" max="22"/>
   </cols>
@@ -1371,11 +1539,11 @@
     <row r="2" ht="15" customHeight="1" s="27">
       <c r="A2" s="29" t="inlineStr">
         <is>
-          <t>Kolom abu-abu dihitung otomatis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" s="27">
+          <t>Kolom abu-abu terisi otomatis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="43.5" customHeight="1" s="27">
       <c r="A4" s="42" t="inlineStr">
         <is>
           <t>ID insiden</t>
@@ -6506,7 +6674,7 @@
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -6514,7 +6682,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -6693,7 +6861,7 @@
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -6713,8 +6881,10 @@
     <col width="34" customWidth="1" style="26" min="5" max="5"/>
     <col width="15" customWidth="1" style="26" min="6" max="6"/>
     <col width="16" customWidth="1" style="26" min="7" max="9"/>
+    <col width="15" customWidth="1" style="27" min="8" max="8"/>
+    <col width="13" customWidth="1" style="27" min="9" max="9"/>
     <col width="22" customWidth="1" style="26" min="10" max="10"/>
-    <col width="9" customWidth="1" style="26" min="11" max="11"/>
+    <col width="18" customWidth="1" style="26" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.15" customHeight="1" s="27">
@@ -6727,7 +6897,7 @@
     <row r="2" ht="15" customHeight="1" s="27">
       <c r="A2" s="29" t="inlineStr">
         <is>
-          <t>Satu baris per perpindahan atau tindakan atas bukti. Hash SHA-256 dihitung saat pengumpulan dan diverifikasi setiap perpindahan.</t>
+          <t>Isi satu baris untuk setiap perpindahan atau tindakan atas bukti. Hash SHA-256 dihitung saat bukti dikumpulkan dan diverifikasi pada setiap perpindahan.</t>
         </is>
       </c>
     </row>
